--- a/paper_info_0023.xlsx
+++ b/paper_info_0023.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>See source_artifacts/Paper_EffectOfIPO/</t>
+          <t>Chyz, J., Henry, E., Omer, T., &amp; Wu, B.</t>
         </is>
       </c>
     </row>
